--- a/Hoàng/2025/T6/NGÂN HÀNG NÔNG NGHIỆP VÀ PHÁT TRIỂN NÔNG THÔN VIỆT NAM - CHI NHÁNH CHỢ MỚI NAM ĐÀ NẴNG (105-2025) (TB 67-2025)/DS- DM ĐKI NH AGRIBANK CHỢ MỚI.xlsx
+++ b/Hoàng/2025/T6/NGÂN HÀNG NÔNG NGHIỆP VÀ PHÁT TRIỂN NÔNG THÔN VIỆT NAM - CHI NHÁNH CHỢ MỚI NAM ĐÀ NẴNG (105-2025) (TB 67-2025)/DS- DM ĐKI NH AGRIBANK CHỢ MỚI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SƯƠNG 2025\1. KSK DOANH NGHIỆP 2025\T5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T6\NGÂN HÀNG NÔNG NGHIỆP VÀ PHÁT TRIỂN NÔNG THÔN VIỆT NAM - CHI NHÁNH CHỢ MỚI NAM ĐÀ NẴNG (105-2025) (TB 67-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DCE6B2-C028-47B5-A9DB-92A265B4B808}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5630EDCD-B556-4C8F-B267-FF3CEE53386B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DOT 1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -166,7 +170,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -371,21 +375,21 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -395,7 +399,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -419,15 +422,16 @@
     <xf numFmtId="165" fontId="18" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -436,7 +440,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -458,9 +461,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -498,9 +501,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -533,26 +536,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -585,26 +571,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -790,25 +759,25 @@
     <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="11" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>26</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
@@ -827,30 +796,30 @@
       <c r="F5" s="25"/>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-    </row>
-    <row r="7" spans="1:7" s="16" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" s="15" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="19" t="s">
         <v>16</v>
       </c>
     </row>
@@ -858,19 +827,19 @@
       <c r="A8" s="2">
         <v>1</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <v>1969</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="13">
         <v>4000000</v>
       </c>
     </row>
@@ -878,19 +847,19 @@
       <c r="A9" s="2">
         <v>2</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>1986</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="13">
         <v>4000000</v>
       </c>
     </row>
@@ -898,19 +867,19 @@
       <c r="A10" s="2">
         <v>3</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <v>1975</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="13">
         <v>4000000</v>
       </c>
     </row>
@@ -918,40 +887,40 @@
       <c r="A11" s="2">
         <v>4</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <v>1984</v>
       </c>
-      <c r="F11" s="14">
-        <v>4000000</v>
-      </c>
-      <c r="G11" s="11"/>
+      <c r="F11" s="13">
+        <v>4000000</v>
+      </c>
+      <c r="G11"/>
     </row>
     <row r="12" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>5</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <v>1979</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="13">
         <v>4000000</v>
       </c>
     </row>
@@ -959,19 +928,19 @@
       <c r="A13" s="2">
         <v>6</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <v>1985</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="13">
         <v>4000000</v>
       </c>
     </row>
@@ -979,19 +948,19 @@
       <c r="A14" s="2">
         <v>7</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <v>1983</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="13">
         <v>4000000</v>
       </c>
     </row>
@@ -999,19 +968,19 @@
       <c r="A15" s="2">
         <v>8</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <v>1983</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="13">
         <v>4000000</v>
       </c>
     </row>
@@ -1019,19 +988,19 @@
       <c r="A16" s="2">
         <v>9</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <v>1993</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="13">
         <v>4000000</v>
       </c>
     </row>
@@ -1039,19 +1008,19 @@
       <c r="A17" s="2">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <v>1975</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="13">
         <v>4000000</v>
       </c>
     </row>
@@ -1059,40 +1028,40 @@
       <c r="A18" s="2">
         <v>11</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <v>2000</v>
       </c>
-      <c r="F18" s="14">
-        <v>4000000</v>
-      </c>
-      <c r="G18" s="11"/>
+      <c r="F18" s="13">
+        <v>4000000</v>
+      </c>
+      <c r="G18"/>
     </row>
     <row r="19" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>12</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="12">
         <v>1993</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="13">
         <v>4000000</v>
       </c>
     </row>
@@ -1100,19 +1069,19 @@
       <c r="A20" s="2">
         <v>13</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="12">
         <v>1983</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="13">
         <v>4000000</v>
       </c>
     </row>
@@ -1120,19 +1089,19 @@
       <c r="A21" s="2">
         <v>14</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="12">
         <v>1995</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="13">
         <v>4000000</v>
       </c>
     </row>
@@ -1144,13 +1113,13 @@
       <c r="C22" s="5"/>
       <c r="D22" s="6"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="18">
+      <c r="F22" s="17">
         <f>SUM(F8:F21)</f>
         <v>56000000</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="3" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="22" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="8"/>
@@ -1167,11 +1136,11 @@
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
     </row>
-    <row r="25" spans="1:7" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+    <row r="25" spans="1:7" s="21" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="20" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="26" t="s">
@@ -1199,7 +1168,7 @@
   <dimension ref="GD1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="186" max="186" width="9.140625" style="28"/>
+    <col min="186" max="186" width="9.140625" style="23"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
